--- a/Proyecto/Fase2/techcore-odoo/2_Clientes_Odoo.xlsx
+++ b/Proyecto/Fase2/techcore-odoo/2_Clientes_Odoo.xlsx
@@ -417,50 +417,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>company_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>street</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_id</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>category_id</t>
         </is>
@@ -469,35 +475,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>techcore_cli_juan_perez</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Juan Pérez</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>juan.perez@gmail.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>+502 5555-1111</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Zona 10 Ciudad de Guatemala</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
@@ -506,35 +517,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>techcore_cli_maria_lopez</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>María López</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>mlopez@estudiante.usac.edu.gt</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>+502 4444-2222</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Zona 1 Ciudad de Guatemala</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
@@ -543,35 +559,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>techcore_cli_techcorp_s_a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>TechCorp S.A.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>compras@techcorp.com.gt</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>+502 2222-3333</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Zona 14 Ciudad de Guatemala</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
@@ -580,35 +601,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>techcore_cli_innova_solutions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Innova Solutions</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>info@innovasolutions.gt</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>+502 2333-4444</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Zona 4 Ciudad de Guatemala</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
@@ -617,35 +643,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>techcore_cli_carlos_ruiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Carlos Ruiz</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>cruiz99@hotmail.com</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>+502 5666-7777</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Mixco Guatemala</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
